--- a/merge/result.xlsx
+++ b/merge/result.xlsx
@@ -413,23 +413,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>transaction_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>지출</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>수익</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -454,32 +454,64 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>결제자</t>
+          <t>결제구분</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>원거래통화</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>원거래금액</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>collect_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>구매항목</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>23787</v>
+          <t>tx_260202_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-67302</t>
+        </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>교촌치킨</t>
+          <t>쿠팡</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>식비</t>
+          <t>기타물품</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>포인트 적립 476원</t>
+          <t>포인트 적립 1,346원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -489,27 +521,51 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>개인카드</t>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>무선 이어폰</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>85589</v>
+          <t>tx_260204_01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-42512</t>
+        </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>이마트 성수점</t>
+          <t>쿠팡</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>소모품·비품</t>
+          <t>기타물품</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -520,27 +576,51 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>개인카드</t>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>책상 정리함, 문구류</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>17000</v>
+          <t>tx_260208_01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-13334</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>넷플릭스</t>
+          <t>GS25 학동역점</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>구독·소프트웨어</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -551,9 +631,737 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>개인카드</t>
-        </is>
-      </c>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>삼각김밥, 커피</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tx_260209_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>-23787</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>교촌치킨</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>포인트 적립 476원</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>허니콤보 치킨</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>tx_260209_03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-2058</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>파리바게뜨</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>포인트 적립 41원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>tx_260215_01</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-22805</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>교촌치킨</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>허니콤보 치킨</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>tx_260215_02</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-14455</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>GS25 학동역점</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>삼각김밥, 커피</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tx_260217_01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-17000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>구독료</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>tx_260218_01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>-4291</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>다이소</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>수납정리함, 문구류</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>tx_260224_01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-12819</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>배달의민족</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>떡볶이, 순대</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>tx_260224_02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-24144</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>포인트 적립 483원</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>tx_260210_01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-130800</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>하이마트 강남점</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>할부 1/6 (원금 120,000 + 수수료 10,800), 총액 720,000</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>냉장고</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tx_260226_01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-7608</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>스타벅스 강남점</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>포인트 적립 152원</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>tx_260227_01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-18415</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>파리바게뜨</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>tx_260227_02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-36252</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>tx_260227_03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-6252</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GS25 학동역점</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>포인트 적립 125원</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/merge/result.xlsx
+++ b/merge/result.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,34 +486,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tx_260202_01</t>
+          <t>tx_260801_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-67302</t>
+          <t>-4500</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>스타벅스 강남점</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>기타물품</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>포인트 적립 1,346원</t>
-        </is>
-      </c>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -538,34 +534,34 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>무선 이어폰</t>
+          <t>아메리카노</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tx_260204_01</t>
+          <t>tx_260802_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-42512</t>
+          <t>-23000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>쿠팡</t>
+          <t>교촌치킨 역삼점</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>기타물품</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -591,39 +587,39 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>책상 정리함, 문구류</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tx_260208_01</t>
+          <t>tx_260803_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-13334</t>
+          <t>-17000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>GS25 학동역점</t>
+          <t>넷플릭스</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>구독료</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>정기결제</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -646,41 +642,37 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>삼각김밥, 커피</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tx_260209_01</t>
+          <t>tx_260804_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-23787</t>
+          <t>-13400</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>교촌치킨</t>
+          <t>카카오T</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>식대</t>
+          <t>교통비</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>포인트 적립 476원</t>
+          <t>심야 택시</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -705,41 +697,37 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>허니콤보 치킨</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tx_260209_03</t>
+          <t>tx_260805_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-2058</t>
+          <t>-62000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>파리바게뜨</t>
+          <t>GS칼텍스 서초주유소</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>식대</t>
+          <t>교통비</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>포인트 적립 41원</t>
+          <t>주유</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -761,7 +749,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>확인됨</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -769,27 +757,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tx_260215_01</t>
+          <t>tx_260807_01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-22805</t>
+          <t>-28900</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>교촌치킨</t>
+          <t>다이소 강남점</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>식대</t>
+          <t>기타물품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -807,7 +795,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>card_excel</t>
+          <t>receipt</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -817,34 +805,34 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>허니콤보 치킨</t>
+          <t>수납함, 건전지</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tx_260215_02</t>
+          <t>tx_260809_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-14455</t>
+          <t>-35800</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GS25 학동역점</t>
+          <t>올리브영 명동점</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>식대</t>
+          <t>기타물품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -870,39 +858,39 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>삼각김밥, 커피</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tx_260217_01</t>
+          <t>tx_260810_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-17000</t>
+          <t>-63430</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>넷플릭스</t>
+          <t>Amazon.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>구독료</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>해외승인</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -913,8 +901,16 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>45.99</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -922,35 +918,39 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>키보드 팜레스트</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tx_260218_01</t>
+          <t>tx_260814_01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4291</t>
+          <t>-8900</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>다이소</t>
+          <t>CU 역삼점</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>기타물품</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -968,7 +968,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>card_excel</t>
+          <t>receipt</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -978,37 +978,41 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>수납정리함, 문구류</t>
+          <t>도시락, 음료</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tx_260224_01</t>
+          <t>tx_260815_01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-12819</t>
+          <t>-49500</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>배달의민족</t>
+          <t>SKT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>통신비</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8월 요금</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1031,41 +1035,37 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>떡볶이, 순대</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tx_260224_02</t>
+          <t>tx_260816_01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-24144</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>기타물품</t>
+          <t>환급·캐시백</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>포인트 적립 483원</t>
+          <t>7월 실적 캐시백</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>확인됨</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -1095,34 +1095,30 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tx_260210_01</t>
+          <t>tx_260818_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-130800</t>
+          <t>-86000</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>하이마트 강남점</t>
+          <t>파고다어학원</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>기타물품</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>할부 1/6 (원금 120,000 + 수수료 10,800), 총액 720,000</t>
-        </is>
-      </c>
+          <t>교육비</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1145,43 +1141,35 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>냉장고</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tx_260226_01</t>
+          <t>tx_260823_01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-7608</t>
+          <t>-32000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>스타벅스 강남점</t>
+          <t>강남세브란스병원</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>포인트 적립 152원</t>
-        </is>
-      </c>
+          <t>의료비</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -1201,7 +1189,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>확인됨</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1209,38 +1197,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tx_260227_01</t>
+          <t>tx_260805_02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-18415</t>
+          <t>-128000</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>파리바게뜨</t>
+          <t>한우명가 역삼점</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>접대비</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>거래처 미팅</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한카드</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1252,7 +1244,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>확인됨</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1260,93 +1252,97 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tx_260227_02</t>
+          <t>tx_260806_01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-36252</t>
+          <t>-94500</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>올리브영</t>
+          <t>오피스디포 강남점</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>기타물품</t>
+          <t>소모품비</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한카드</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>card_excel</t>
+          <t>receipt</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>A4용지, 토너</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tx_260227_03</t>
+          <t>tx_260811_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-6252</t>
+          <t>-186000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>GS25 학동역점</t>
+          <t>아웃백 강남점</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>식대</t>
+          <t>복리후생비</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>포인트 적립 125원</t>
+          <t>팀 회식</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한카드</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1358,10 +1354,246 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>확인 필요</t>
+          <t>확인됨</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>tx_260813_01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-330000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>디자인스튜디오 모노</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>외주용역비</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>배너 디자인 외주</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>신한카드</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tx_260817_01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-142380</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Meta Ads</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>광고선전비</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SNS 광고 집행</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>신한카드</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>103.20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tx_260819_01</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-59400</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>코레일</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>여비교통비</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>KTX 서울-부산 출장</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>신한카드</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tx_260820_01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-13200</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>클라우드 사용료</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>신한카드</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9.60</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/merge/result.xlsx
+++ b/merge/result.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FAF7F2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E5B45"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,71 +423,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>금액</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>결제처</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>카테고리</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>결제수단</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>결제구분</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>원거래통화</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>원거래금액</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>collect_status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>구매항목</t>
         </is>
@@ -486,22 +511,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tx_260801_01</t>
+          <t>tx_260701_01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4500</t>
+          <t>-14857</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>스타벅스 강남점</t>
+          <t>GS25 학동역점</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -534,45 +559,49 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>아메리카노</t>
+          <t>생수, 과자</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tx_260802_01</t>
+          <t>tx_260702_01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-23000</t>
+          <t>-12000</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>교촌치킨 역삼점</t>
+          <t>모두의주차장 강남점</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>여비교통비</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>결제시각 12:34, 승인번호 30711022, 사용자 김규은</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -592,42 +621,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tx_260803_01</t>
+          <t>tx_260703_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-17000</t>
+          <t>-23800</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>넷플릭스</t>
+          <t>스타벅스 테헤란로점</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>구독료</t>
+          <t>복리후생비</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>정기결제</t>
+          <t>결제시각 08:15, 승인번호 30718334, 사용자 이지은</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -647,34 +676,30 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tx_260804_01</t>
+          <t>tx_260705_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-13400</t>
+          <t>-19588</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>카카오T</t>
+          <t>파리바게뜨</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>교통비</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>심야 택시</t>
-        </is>
-      </c>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -697,39 +722,39 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>샌드위치, 커피</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>tx_260805_01</t>
+          <t>tx_260707_01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-62000</t>
+          <t>-49790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>GS칼텍스 서초주유소</t>
+          <t>이마트 성수점</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>교통비</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>주유</t>
-        </is>
-      </c>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -752,50 +777,58 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>고기, 채소</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>tx_260807_01</t>
+          <t>tx_260707_02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-28900</t>
+          <t>-148000</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>다이소 강남점</t>
+          <t>오피스디포 역삼점</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>기타물품</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>소모품비</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>결제시각 14:02, 승인번호 30742190, 사용자 김규은</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>receipt</t>
+          <t>card_excel</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -803,36 +836,32 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>수납함, 건전지</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tx_260809_01</t>
+          <t>tx_260708_01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-35800</t>
+          <t>-55561</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>올리브영 명동점</t>
+          <t>SK주유소</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>기타물품</t>
+          <t>교통비</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -858,39 +887,39 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>휘발유</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tx_260810_01</t>
+          <t>tx_260709_01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-63430</t>
+          <t>-19460</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Amazon.com</t>
+          <t>파리바게뜨</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>기타물품</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>해외승인</t>
-        </is>
-      </c>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>하나카드</t>
@@ -901,16 +930,8 @@
           <t>개인결제</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>45.99</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -923,52 +944,64 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>키보드 팜레스트</t>
+          <t>식빵, 케이크</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tx_260814_01</t>
+          <t>tx_260709_02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-8900</t>
+          <t>-55890</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CU 역삼점</t>
+          <t>APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>식대</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>지급수수료</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>결제시각 19:22, 승인번호 30755401, 사용자 이지은</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>개인결제</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>39.99</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>receipt</t>
+          <t>card_excel</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -976,41 +1009,37 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>도시락, 음료</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tx_260815_01</t>
+          <t>tx_260710_01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-49500</t>
+          <t>-17366</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SKT</t>
+          <t>배달의민족</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>통신비</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8월 요금</t>
+          <t>포인트 적립 347원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1035,47 +1064,51 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>짜장면, 탕수육</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tx_260816_01</t>
+          <t>tx_260710_02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12000</t>
+          <t>-64300</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>교보문고 강남점</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>환급·캐시백</t>
+          <t>교육훈련비·도서인쇄비</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7월 실적 캐시백</t>
+          <t>결제시각 11:45, 승인번호 30761877, 사용자 박서준</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1095,27 +1128,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tx_260818_01</t>
+          <t>tx_260711_01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-86000</t>
+          <t>-13355</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>파고다어학원</t>
+          <t>파리바게뜨</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>교육비</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -1141,43 +1174,51 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>식빵, 케이크</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>tx_260823_01</t>
+          <t>tx_260711_02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-32000</t>
+          <t>-47200</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>강남세브란스병원</t>
+          <t>KTX 코레일</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>의료비</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>여비교통비</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>결제시각 09:30, 승인번호 30768245, 사용자 박서준</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>하나카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>개인결제</t>
+          <t>법인결제</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1197,42 +1238,42 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>tx_260805_02</t>
+          <t>tx_260712_01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-128000</t>
+          <t>-26419</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>한우명가 역삼점</t>
+          <t>교촌치킨</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>접대비</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>거래처 미팅</t>
+          <t>포인트 적립 528원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>법인결제</t>
+          <t>개인결제</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1247,50 +1288,54 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>허니콤보 치킨</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tx_260806_01</t>
+          <t>tx_260712_02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-94500</t>
+          <t>-26205</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>오피스디포 강남점</t>
+          <t>배달의민족</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>소모품비</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>법인결제</t>
+          <t>개인결제</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>receipt</t>
+          <t>card_excel</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1300,49 +1345,45 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>A4용지, 토너</t>
+          <t>짜장면, 탕수육</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>tx_260811_01</t>
+          <t>tx_260714_01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-186000</t>
+          <t>-14207</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>아웃백 강남점</t>
+          <t>CGV</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>복리후생비</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>팀 회식</t>
-        </is>
-      </c>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>법인결제</t>
+          <t>개인결제</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1357,54 +1398,58 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>영화 티켓, 팝콘</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tx_260813_01</t>
+          <t>tx_260715_01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-330000</t>
+          <t>-48559</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>디자인스튜디오 모노</t>
+          <t>쿠팡</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>외주용역비</t>
+          <t>기타물품</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>배너 디자인 외주</t>
+          <t>포인트 적립 971원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>법인결제</t>
+          <t>개인결제</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>card_excel</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1412,59 +1457,51 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>샴푸, 바디워시</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tx_260817_01</t>
+          <t>tx_260716_01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-142380</t>
+          <t>-14470</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>CGV</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>광고선전비</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>SNS 광고 집행</t>
-        </is>
-      </c>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>법인결제</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>103.20</t>
-        </is>
-      </c>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1475,47 +1512,51 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>영화 티켓, 팝콘</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tx_260819_01</t>
+          <t>tx_260718_01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-59400</t>
+          <t>-7568</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>코레일</t>
+          <t>스타벅스 강남점</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>여비교통비</t>
+          <t>식대</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>KTX 서울-부산 출장</t>
+          <t>포인트 적립 151원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>하나카드</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>법인결제</t>
+          <t>개인결제</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1530,42 +1571,46 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>아메리카노</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tx_260820_01</t>
+          <t>tx_260718_02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-13200</t>
+          <t>-8700</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AWS</t>
+          <t>GS25 학동역점</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>지급수수료</t>
+          <t>복리후생비</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>클라우드 사용료</t>
+          <t>결제시각 19:42, 승인번호 30812456, 사용자 김규은</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>신한카드</t>
+          <t>신한법인카드</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1573,16 +1618,8 @@
           <t>법인결제</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>9.60</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>card_excel</t>
@@ -1593,7 +1630,813 @@
           <t>확인됨</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>삼각김밥, 커피</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>tx_260719_01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-5777</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>스타벅스 강남점</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>카페라떼, 베이글</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tx_260720_01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-17000</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>넷플릭스</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>구독료</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>포인트 적립 340원</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>OTT 구독료</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>tx_260720_03</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-17336</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>파리바게뜨</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>식빵, 케이크</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>tx_260721_01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-68389</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>무신사</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>포인트 적립 1,368원</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>티셔츠</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>tx_260722_01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>-14758</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>카카오T</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>교통비</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>포인트 적립 295원</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>택시비</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>tx_260723_01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>-9498</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>다이소</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>포인트 적립 190원</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>수납정리함, 문구류</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tx_260723_02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>-21678</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>올리브영</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>선크림</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>tx_260210_01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>-121800</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>하이마트 강남점</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>할부 6/6 (원금 120,000 + 수수료 1,800), 총액 720,000 (완납)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>냉장고</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>tx_260725_01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>-7558</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>다이소</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>기타물품</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>수납정리함, 문구류</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>tx_260725_02</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-330000</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>법무법인 해온</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>외주용역비</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>결제시각 10:11, 승인번호 30851028, 사용자 박서준</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>신한법인카드</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>tx_260726_01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-30544</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>배달의민족</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>포인트 적립 611원</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>치킨, 콜라</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>tx_260726_02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-65182</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>SK주유소</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>교통비</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>휘발유</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>tx_260727_01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-23066</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>교촌치킨</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>식대</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>포인트 적립 461원</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>하나카드</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>개인결제</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>허니콤보 치킨</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>tx_260731_01</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-31500</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>배달의민족</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>복리후생비</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>결제시각 23:59, 승인번호 30887514, 사용자 이지은</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>신한법인카드</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>법인결제</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>card_excel</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>확인됨</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>치킨, 콜라</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
